--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/127.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/127.xlsx
@@ -426,13 +426,13 @@
         <v>-12.06891955126177</v>
       </c>
       <c r="E2">
-        <v>-26.08560185526555</v>
+        <v>-31.28466587941376</v>
       </c>
       <c r="F2">
-        <v>-3.297052344889447</v>
+        <v>-4.028552120340384</v>
       </c>
       <c r="G2">
-        <v>-14.83641789400836</v>
+        <v>-17.97513618815476</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.83952508113959</v>
       </c>
       <c r="E3">
-        <v>-26.44831450938392</v>
+        <v>-31.47377495397408</v>
       </c>
       <c r="F3">
-        <v>-3.213398005982933</v>
+        <v>-3.925189264186464</v>
       </c>
       <c r="G3">
-        <v>-15.01647515534378</v>
+        <v>-17.66487848130534</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.49776366074851</v>
       </c>
       <c r="E4">
-        <v>-26.24036245447769</v>
+        <v>-31.43475988616099</v>
       </c>
       <c r="F4">
-        <v>-3.175241746675182</v>
+        <v>-3.968240346477357</v>
       </c>
       <c r="G4">
-        <v>-14.55334638712744</v>
+        <v>-17.72009010453653</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.06698607623654</v>
       </c>
       <c r="E5">
-        <v>-26.87736930771466</v>
+        <v>-32.46615606919998</v>
       </c>
       <c r="F5">
-        <v>-3.157710178962334</v>
+        <v>-3.990913590659383</v>
       </c>
       <c r="G5">
-        <v>-14.84137543595342</v>
+        <v>-17.61798129319602</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.56071135577464</v>
       </c>
       <c r="E6">
-        <v>-26.97893845123269</v>
+        <v>-32.47638815622031</v>
       </c>
       <c r="F6">
-        <v>-3.218015325886137</v>
+        <v>-4.011558991439355</v>
       </c>
       <c r="G6">
-        <v>-14.23105319197</v>
+        <v>-17.59733011012205</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.989027814577682</v>
       </c>
       <c r="E7">
-        <v>-27.41892045734394</v>
+        <v>-32.99986843032198</v>
       </c>
       <c r="F7">
-        <v>-3.280313524781077</v>
+        <v>-4.023020282824489</v>
       </c>
       <c r="G7">
-        <v>-13.97375262683954</v>
+        <v>-17.32282795036953</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.373493236744538</v>
       </c>
       <c r="E8">
-        <v>-27.52201569660256</v>
+        <v>-32.82936006274817</v>
       </c>
       <c r="F8">
-        <v>-3.160004756668088</v>
+        <v>-3.819955954437023</v>
       </c>
       <c r="G8">
-        <v>-13.94510813156099</v>
+        <v>-16.92421343834974</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.735470356778459</v>
       </c>
       <c r="E9">
-        <v>-28.63531386054427</v>
+        <v>-33.54801983081745</v>
       </c>
       <c r="F9">
-        <v>-3.086363722926615</v>
+        <v>-3.947486429567618</v>
       </c>
       <c r="G9">
-        <v>-13.79232148910532</v>
+        <v>-16.81154729728449</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.084529096198345</v>
       </c>
       <c r="E10">
-        <v>-28.6692774156018</v>
+        <v>-33.90656402461175</v>
       </c>
       <c r="F10">
-        <v>-3.131864287627586</v>
+        <v>-3.877834813238028</v>
       </c>
       <c r="G10">
-        <v>-13.46849882190874</v>
+        <v>-16.76923521474707</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.449812403726739</v>
       </c>
       <c r="E11">
-        <v>-29.03926279897648</v>
+        <v>-34.24550219018985</v>
       </c>
       <c r="F11">
-        <v>-3.050341338048476</v>
+        <v>-3.902349518156476</v>
       </c>
       <c r="G11">
-        <v>-13.29510568874387</v>
+        <v>-16.41452184712355</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.847412626751884</v>
       </c>
       <c r="E12">
-        <v>-29.24740957826504</v>
+        <v>-34.63933225345191</v>
       </c>
       <c r="F12">
-        <v>-3.048035163199082</v>
+        <v>-3.82723399043802</v>
       </c>
       <c r="G12">
-        <v>-13.08276067676394</v>
+        <v>-16.23667768548113</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.289466352798995</v>
       </c>
       <c r="E13">
-        <v>-30.12529954939202</v>
+        <v>-34.83285885440671</v>
       </c>
       <c r="F13">
-        <v>-3.054101297689783</v>
+        <v>-3.838863440405922</v>
       </c>
       <c r="G13">
-        <v>-13.13621274504101</v>
+        <v>-16.03260076098552</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.800964950647258</v>
       </c>
       <c r="E14">
-        <v>-30.55123649336847</v>
+        <v>-35.69424480201273</v>
       </c>
       <c r="F14">
-        <v>-2.815384864653229</v>
+        <v>-3.819814303611145</v>
       </c>
       <c r="G14">
-        <v>-12.4908814819798</v>
+        <v>-15.69676246875416</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.381488100988721</v>
       </c>
       <c r="E15">
-        <v>-31.47515840278342</v>
+        <v>-36.42714209236212</v>
       </c>
       <c r="F15">
-        <v>-2.678941984635915</v>
+        <v>-3.62901229788732</v>
       </c>
       <c r="G15">
-        <v>-12.30856973913214</v>
+        <v>-15.23483046275026</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.033071962002006</v>
       </c>
       <c r="E16">
-        <v>-31.61889896049789</v>
+        <v>-36.61612436965022</v>
       </c>
       <c r="F16">
-        <v>-2.58173804012181</v>
+        <v>-3.454775983484681</v>
       </c>
       <c r="G16">
-        <v>-12.00184438437312</v>
+        <v>-15.19403461006982</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.756231398142318</v>
       </c>
       <c r="E17">
-        <v>-32.76379908030213</v>
+        <v>-37.1949878808657</v>
       </c>
       <c r="F17">
-        <v>-2.509908645890258</v>
+        <v>-3.513582613776821</v>
       </c>
       <c r="G17">
-        <v>-11.62390588451884</v>
+        <v>-15.24193820402308</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.535340628662515</v>
       </c>
       <c r="E18">
-        <v>-33.50047085373691</v>
+        <v>-37.82019805931269</v>
       </c>
       <c r="F18">
-        <v>-2.269626598462414</v>
+        <v>-3.388465172890581</v>
       </c>
       <c r="G18">
-        <v>-11.45919300175795</v>
+        <v>-14.74855436012334</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.364934858793522</v>
       </c>
       <c r="E19">
-        <v>-34.01183972410507</v>
+        <v>-38.40473574845978</v>
       </c>
       <c r="F19">
-        <v>-2.240404281593856</v>
+        <v>-3.170038771018199</v>
       </c>
       <c r="G19">
-        <v>-11.34365496243738</v>
+        <v>-14.80401261899721</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.232767562384503</v>
       </c>
       <c r="E20">
-        <v>-34.23216583423726</v>
+        <v>-39.23397405908535</v>
       </c>
       <c r="F20">
-        <v>-2.042448494979455</v>
+        <v>-3.18095499665229</v>
       </c>
       <c r="G20">
-        <v>-11.05959360244022</v>
+        <v>-14.70913238384169</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.1218255122295</v>
       </c>
       <c r="E21">
-        <v>-35.54251828038574</v>
+        <v>-39.4719861244545</v>
       </c>
       <c r="F21">
-        <v>-1.99235131956035</v>
+        <v>-2.950768262762364</v>
       </c>
       <c r="G21">
-        <v>-11.20761802513765</v>
+        <v>-14.39446171978843</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.029031559834641</v>
       </c>
       <c r="E22">
-        <v>-35.60192733089237</v>
+        <v>-39.84411574027181</v>
       </c>
       <c r="F22">
-        <v>-1.800067364552917</v>
+        <v>-2.793636906860131</v>
       </c>
       <c r="G22">
-        <v>-10.98869826971672</v>
+        <v>-14.33209600764687</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.942547533698137</v>
       </c>
       <c r="E23">
-        <v>-35.73669471736063</v>
+        <v>-40.61540543325822</v>
       </c>
       <c r="F23">
-        <v>-1.563506343498449</v>
+        <v>-2.756931947242085</v>
       </c>
       <c r="G23">
-        <v>-10.88327063647309</v>
+        <v>-14.08032570883976</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.859164842486075</v>
       </c>
       <c r="E24">
-        <v>-36.28532840033791</v>
+        <v>-40.5474987012762</v>
       </c>
       <c r="F24">
-        <v>-1.658679131140889</v>
+        <v>-2.498546758593461</v>
       </c>
       <c r="G24">
-        <v>-11.07697727706693</v>
+        <v>-14.11673674395343</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.786401174851255</v>
       </c>
       <c r="E25">
-        <v>-36.80039250549633</v>
+        <v>-40.66143510730919</v>
       </c>
       <c r="F25">
-        <v>-1.40223646405183</v>
+        <v>-2.448396567660576</v>
       </c>
       <c r="G25">
-        <v>-10.73613343998019</v>
+        <v>-14.40025848502769</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.724347382473126</v>
       </c>
       <c r="E26">
-        <v>-36.95043669902948</v>
+        <v>-40.80431525496221</v>
       </c>
       <c r="F26">
-        <v>-1.411793338777928</v>
+        <v>-2.510434659191036</v>
       </c>
       <c r="G26">
-        <v>-11.02134355927948</v>
+        <v>-14.42690341080052</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.683759090896654</v>
       </c>
       <c r="E27">
-        <v>-36.84644935039135</v>
+        <v>-40.70878483153339</v>
       </c>
       <c r="F27">
-        <v>-1.374218593386942</v>
+        <v>-2.424100551736466</v>
       </c>
       <c r="G27">
-        <v>-10.92354673350387</v>
+        <v>-14.28863682108009</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.673304729363592</v>
       </c>
       <c r="E28">
-        <v>-36.54395181515297</v>
+        <v>-40.84116571219962</v>
       </c>
       <c r="F28">
-        <v>-1.346466628658353</v>
+        <v>-2.350276448798974</v>
       </c>
       <c r="G28">
-        <v>-11.04160078743428</v>
+        <v>-14.78066003076319</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.696754550684487</v>
       </c>
       <c r="E29">
-        <v>-36.66439790257198</v>
+        <v>-40.90843845782057</v>
       </c>
       <c r="F29">
-        <v>-1.172314807730799</v>
+        <v>-2.465638206782445</v>
       </c>
       <c r="G29">
-        <v>-11.01969821814646</v>
+        <v>-14.3633359706282</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.766736200538346</v>
       </c>
       <c r="E30">
-        <v>-36.44279249853263</v>
+        <v>-41.00159143239535</v>
       </c>
       <c r="F30">
-        <v>-1.114527897711505</v>
+        <v>-2.193677733136742</v>
       </c>
       <c r="G30">
-        <v>-10.97290034640332</v>
+        <v>-14.40686302337854</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.884848110469612</v>
       </c>
       <c r="E31">
-        <v>-36.02685216092811</v>
+        <v>-40.39740922300298</v>
       </c>
       <c r="F31">
-        <v>-1.217455860978955</v>
+        <v>-2.253972111284309</v>
       </c>
       <c r="G31">
-        <v>-10.94507521114575</v>
+        <v>-14.82552785445693</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.051333712973598</v>
       </c>
       <c r="E32">
-        <v>-35.56751998538208</v>
+        <v>-40.25404452863115</v>
       </c>
       <c r="F32">
-        <v>-1.409557575157772</v>
+        <v>-2.489553173701266</v>
       </c>
       <c r="G32">
-        <v>-11.323559951014</v>
+        <v>-14.71673836221817</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.269786865829448</v>
       </c>
       <c r="E33">
-        <v>-35.90191609153049</v>
+        <v>-40.05101718920826</v>
       </c>
       <c r="F33">
-        <v>-1.325184213345628</v>
+        <v>-2.4468947375593</v>
       </c>
       <c r="G33">
-        <v>-11.27606024361654</v>
+        <v>-14.83854491951734</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.527867454844768</v>
       </c>
       <c r="E34">
-        <v>-35.42942643475518</v>
+        <v>-39.60688483666899</v>
       </c>
       <c r="F34">
-        <v>-1.327535120034773</v>
+        <v>-2.206547249106635</v>
       </c>
       <c r="G34">
-        <v>-11.9284595214041</v>
+        <v>-14.8180940244485</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.822102028140971</v>
       </c>
       <c r="E35">
-        <v>-34.4519326778295</v>
+        <v>-39.39987696859335</v>
       </c>
       <c r="F35">
-        <v>-1.317026451162858</v>
+        <v>-2.461963568983626</v>
       </c>
       <c r="G35">
-        <v>-11.94046024898396</v>
+        <v>-15.24543745065809</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.146329882665621</v>
       </c>
       <c r="E36">
-        <v>-34.56402599494136</v>
+        <v>-39.05912288493818</v>
       </c>
       <c r="F36">
-        <v>-1.299202469756822</v>
+        <v>-2.396575559676244</v>
       </c>
       <c r="G36">
-        <v>-12.04610306768764</v>
+        <v>-15.0752456150297</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.485075069506276</v>
       </c>
       <c r="E37">
-        <v>-34.28449461563289</v>
+        <v>-38.69625852694056</v>
       </c>
       <c r="F37">
-        <v>-1.236582864309596</v>
+        <v>-2.2415416300379</v>
       </c>
       <c r="G37">
-        <v>-11.67446453599459</v>
+        <v>-14.86341373760835</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.834386887382149</v>
       </c>
       <c r="E38">
-        <v>-33.62826212599636</v>
+        <v>-38.21061365317297</v>
       </c>
       <c r="F38">
-        <v>-1.176409427802837</v>
+        <v>-2.429332520252548</v>
       </c>
       <c r="G38">
-        <v>-11.70535854696707</v>
+        <v>-15.3148761433443</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.183134724074955</v>
       </c>
       <c r="E39">
-        <v>-33.64684245484983</v>
+        <v>-37.56987080887968</v>
       </c>
       <c r="F39">
-        <v>-1.22688765222723</v>
+        <v>-2.292809288597161</v>
       </c>
       <c r="G39">
-        <v>-11.81867521023079</v>
+        <v>-15.37815060023639</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.518605794560244</v>
       </c>
       <c r="E40">
-        <v>-32.96880989134037</v>
+        <v>-37.11017409117604</v>
       </c>
       <c r="F40">
-        <v>-1.214438946897959</v>
+        <v>-2.355441319555429</v>
       </c>
       <c r="G40">
-        <v>-12.02197912234297</v>
+        <v>-15.08302208650144</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.838700033835777</v>
       </c>
       <c r="E41">
-        <v>-32.29495484510299</v>
+        <v>-36.58185061412316</v>
       </c>
       <c r="F41">
-        <v>-1.163369268147967</v>
+        <v>-2.150669725950794</v>
       </c>
       <c r="G41">
-        <v>-11.96417699722729</v>
+        <v>-15.40696558861021</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.130870177337398</v>
       </c>
       <c r="E42">
-        <v>-31.52756190400018</v>
+        <v>-36.56459259967993</v>
       </c>
       <c r="F42">
-        <v>-1.099681897118533</v>
+        <v>-2.183411775913847</v>
       </c>
       <c r="G42">
-        <v>-11.7821996194791</v>
+        <v>-15.40076824736069</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.390983281101846</v>
       </c>
       <c r="E43">
-        <v>-31.22330052813582</v>
+        <v>-35.89074887462757</v>
       </c>
       <c r="F43">
-        <v>-1.006309980209778</v>
+        <v>-2.101615465091813</v>
       </c>
       <c r="G43">
-        <v>-12.07940053472163</v>
+        <v>-15.37924308026435</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.62225244086295</v>
       </c>
       <c r="E44">
-        <v>-31.06038188299887</v>
+        <v>-35.35265747914015</v>
       </c>
       <c r="F44">
-        <v>-1.069952619399461</v>
+        <v>-1.963763532122336</v>
       </c>
       <c r="G44">
-        <v>-12.12919113963227</v>
+        <v>-15.2638076678555</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.816479641942677</v>
       </c>
       <c r="E45">
-        <v>-30.07600484558152</v>
+        <v>-34.77993684291607</v>
       </c>
       <c r="F45">
-        <v>-1.0231531746109</v>
+        <v>-2.060878012956939</v>
       </c>
       <c r="G45">
-        <v>-11.89333794377797</v>
+        <v>-15.31992141474615</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.980075459132786</v>
       </c>
       <c r="E46">
-        <v>-29.71593455604663</v>
+        <v>-34.41688455324713</v>
       </c>
       <c r="F46">
-        <v>-0.9154993753104793</v>
+        <v>-1.9630130312554</v>
       </c>
       <c r="G46">
-        <v>-12.14635631825339</v>
+        <v>-15.4944384781216</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.117553150105929</v>
       </c>
       <c r="E47">
-        <v>-29.32190297569122</v>
+        <v>-33.85899466939817</v>
       </c>
       <c r="F47">
-        <v>-0.9244010114209629</v>
+        <v>-2.067847896284094</v>
       </c>
       <c r="G47">
-        <v>-11.74107933333581</v>
+        <v>-15.3434958095313</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.225772761075833</v>
       </c>
       <c r="E48">
-        <v>-28.84347422525486</v>
+        <v>-33.52100069065068</v>
       </c>
       <c r="F48">
-        <v>-0.9178196324057207</v>
+        <v>-2.014310511041162</v>
       </c>
       <c r="G48">
-        <v>-11.88026459944339</v>
+        <v>-15.3681361999801</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.314855009222592</v>
       </c>
       <c r="E49">
-        <v>-28.57749430441434</v>
+        <v>-33.33513173924285</v>
       </c>
       <c r="F49">
-        <v>-0.8187808540944147</v>
+        <v>-1.857243767796348</v>
       </c>
       <c r="G49">
-        <v>-11.74911071681408</v>
+        <v>-15.58099103597308</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.385181071675863</v>
       </c>
       <c r="E50">
-        <v>-27.85070139702729</v>
+        <v>-32.97782834732665</v>
       </c>
       <c r="F50">
-        <v>-0.8942426393872412</v>
+        <v>-1.913875933656139</v>
       </c>
       <c r="G50">
-        <v>-11.97528387751155</v>
+        <v>-15.45897591430493</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.434717481612937</v>
       </c>
       <c r="E51">
-        <v>-27.3763301593018</v>
+        <v>-32.16973348184289</v>
       </c>
       <c r="F51">
-        <v>-0.6748329654077362</v>
+        <v>-1.961081278472071</v>
       </c>
       <c r="G51">
-        <v>-12.10192879711637</v>
+        <v>-15.41680452995292</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.473175050792241</v>
       </c>
       <c r="E52">
-        <v>-26.80679304030511</v>
+        <v>-32.07233506288592</v>
       </c>
       <c r="F52">
-        <v>-0.9851302824550002</v>
+        <v>-1.913969539172655</v>
       </c>
       <c r="G52">
-        <v>-11.89311944777238</v>
+        <v>-15.76580389597566</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.494623346576185</v>
       </c>
       <c r="E53">
-        <v>-26.14512864609638</v>
+        <v>-31.77818576948069</v>
       </c>
       <c r="F53">
-        <v>-0.8014911696631835</v>
+        <v>-1.822125960122065</v>
       </c>
       <c r="G53">
-        <v>-12.28954072337241</v>
+        <v>-15.85700114921873</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.502024518503118</v>
       </c>
       <c r="E54">
-        <v>-26.14466221327359</v>
+        <v>-30.80711791717189</v>
       </c>
       <c r="F54">
-        <v>-0.750479476631387</v>
+        <v>-1.846076546839208</v>
       </c>
       <c r="G54">
-        <v>-11.88970296477585</v>
+        <v>-15.72454787746526</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.505158549861981</v>
       </c>
       <c r="E55">
-        <v>-25.79524063036774</v>
+        <v>-30.85965727260888</v>
       </c>
       <c r="F55">
-        <v>-0.8877855154824191</v>
+        <v>-1.890170543690225</v>
       </c>
       <c r="G55">
-        <v>-12.21745359425478</v>
+        <v>-15.89610862367414</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.498190973652735</v>
       </c>
       <c r="E56">
-        <v>-25.04782052387575</v>
+        <v>-30.47447659470146</v>
       </c>
       <c r="F56">
-        <v>-0.7488301971324133</v>
+        <v>-1.738773146950171</v>
       </c>
       <c r="G56">
-        <v>-12.22457126716421</v>
+        <v>-15.79039628351414</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.490569526050933</v>
       </c>
       <c r="E57">
-        <v>-24.46209411030165</v>
+        <v>-30.1492008352045</v>
       </c>
       <c r="F57">
-        <v>-0.6755229954542682</v>
+        <v>-1.870055298048045</v>
       </c>
       <c r="G57">
-        <v>-12.36164109467219</v>
+        <v>-15.6949664977991</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.488285204014772</v>
       </c>
       <c r="E58">
-        <v>-24.56510330855412</v>
+        <v>-29.54902632530892</v>
       </c>
       <c r="F58">
-        <v>-0.8089804393518938</v>
+        <v>-1.952732163419255</v>
       </c>
       <c r="G58">
-        <v>-12.14680986299227</v>
+        <v>-15.89692136260403</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.488115163167292</v>
       </c>
       <c r="E59">
-        <v>-24.15018640607533</v>
+        <v>-29.73602513098166</v>
       </c>
       <c r="F59">
-        <v>-0.903337285102577</v>
+        <v>-1.829360921018116</v>
       </c>
       <c r="G59">
-        <v>-12.46251341725378</v>
+        <v>-15.68859700818155</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.502501185073283</v>
       </c>
       <c r="E60">
-        <v>-23.93411932574736</v>
+        <v>-29.18858470090541</v>
       </c>
       <c r="F60">
-        <v>-0.9633765260900824</v>
+        <v>-1.911698155754179</v>
       </c>
       <c r="G60">
-        <v>-12.22972909711439</v>
+        <v>-16.05564050266608</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.53041038276608</v>
       </c>
       <c r="E61">
-        <v>-23.83772169954608</v>
+        <v>-29.47016068622834</v>
       </c>
       <c r="F61">
-        <v>-0.9388278581081191</v>
+        <v>-1.859142385883564</v>
       </c>
       <c r="G61">
-        <v>-12.25444894065613</v>
+        <v>-15.87242663615897</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.570024696225241</v>
       </c>
       <c r="E62">
-        <v>-23.34803063425264</v>
+        <v>-28.9926919722816</v>
       </c>
       <c r="F62">
-        <v>-1.006492221038394</v>
+        <v>-1.889916234897566</v>
       </c>
       <c r="G62">
-        <v>-12.37840569728306</v>
+        <v>-16.01489927398704</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.632856571815202</v>
       </c>
       <c r="E63">
-        <v>-23.59106024882228</v>
+        <v>-28.98273838641274</v>
       </c>
       <c r="F63">
-        <v>-1.01993662398583</v>
+        <v>-2.052557062395818</v>
       </c>
       <c r="G63">
-        <v>-12.51226098507241</v>
+        <v>-15.82678248953627</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.709111486014871</v>
       </c>
       <c r="E64">
-        <v>-23.42859218684909</v>
+        <v>-28.7476200159345</v>
       </c>
       <c r="F64">
-        <v>-1.041094784188135</v>
+        <v>-1.964203395213223</v>
       </c>
       <c r="G64">
-        <v>-12.45853414151558</v>
+        <v>-16.02595815136098</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.800371418361895</v>
       </c>
       <c r="E65">
-        <v>-23.11341039591524</v>
+        <v>-28.6078803650058</v>
       </c>
       <c r="F65">
-        <v>-1.249092868826674</v>
+        <v>-2.15797426970868</v>
       </c>
       <c r="G65">
-        <v>-12.33660012821315</v>
+        <v>-16.23936253791348</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.909001481127381</v>
       </c>
       <c r="E66">
-        <v>-22.81655533929042</v>
+        <v>-28.58451343912623</v>
       </c>
       <c r="F66">
-        <v>-1.081293797511189</v>
+        <v>-2.213566834477958</v>
       </c>
       <c r="G66">
-        <v>-12.34796523104946</v>
+        <v>-16.04597702023695</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.020164279046629</v>
       </c>
       <c r="E67">
-        <v>-23.04789243397226</v>
+        <v>-28.19436276099539</v>
       </c>
       <c r="F67">
-        <v>-1.444995132649534</v>
+        <v>-2.330027836004943</v>
       </c>
       <c r="G67">
-        <v>-12.4676480733852</v>
+        <v>-16.02187293816552</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.134377714641008</v>
       </c>
       <c r="E68">
-        <v>-23.11571991765915</v>
+        <v>-28.62652409249538</v>
       </c>
       <c r="F68">
-        <v>-1.223457382812237</v>
+        <v>-2.495621793294176</v>
       </c>
       <c r="G68">
-        <v>-12.46414220565911</v>
+        <v>-15.51037875489319</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.245169740218966</v>
       </c>
       <c r="E69">
-        <v>-22.47025840344986</v>
+        <v>-28.35592512816704</v>
       </c>
       <c r="F69">
-        <v>-1.556461907105042</v>
+        <v>-2.38328854653534</v>
       </c>
       <c r="G69">
-        <v>-12.10458385463886</v>
+        <v>-15.84626173948934</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.339484922254691</v>
       </c>
       <c r="E70">
-        <v>-22.6957492381878</v>
+        <v>-28.49974040570264</v>
       </c>
       <c r="F70">
-        <v>-1.530935765587775</v>
+        <v>-2.569870020341901</v>
       </c>
       <c r="G70">
-        <v>-12.23670772711118</v>
+        <v>-15.70462170386439</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.419800519580312</v>
       </c>
       <c r="E71">
-        <v>-22.38487855450925</v>
+        <v>-28.3651722720907</v>
       </c>
       <c r="F71">
-        <v>-1.675707051472836</v>
+        <v>-2.599169375378919</v>
       </c>
       <c r="G71">
-        <v>-12.33059148805937</v>
+        <v>-15.65768644448137</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.474714168149928</v>
       </c>
       <c r="E72">
-        <v>-22.93675915335002</v>
+        <v>-28.57028497379412</v>
       </c>
       <c r="F72">
-        <v>-1.929724258806499</v>
+        <v>-2.647539404763188</v>
       </c>
       <c r="G72">
-        <v>-12.01793363569398</v>
+        <v>-15.34931078277103</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.495269851928288</v>
       </c>
       <c r="E73">
-        <v>-22.67317932373357</v>
+        <v>-27.92629068516332</v>
       </c>
       <c r="F73">
-        <v>-1.80623455986676</v>
+        <v>-2.881690705042913</v>
       </c>
       <c r="G73">
-        <v>-12.11905755973656</v>
+        <v>-15.73840913163819</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.484912446168158</v>
       </c>
       <c r="E74">
-        <v>-22.50064446404133</v>
+        <v>-28.37922865541051</v>
       </c>
       <c r="F74">
-        <v>-1.968151394254965</v>
+        <v>-2.787672661559975</v>
       </c>
       <c r="G74">
-        <v>-11.75879075197091</v>
+        <v>-15.30672392495384</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.42960287116721</v>
       </c>
       <c r="E75">
-        <v>-22.72707722137286</v>
+        <v>-28.86174661787581</v>
       </c>
       <c r="F75">
-        <v>-2.080763800828544</v>
+        <v>-2.81923180287183</v>
       </c>
       <c r="G75">
-        <v>-11.89412585361632</v>
+        <v>-15.41392270006099</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.326666344820113</v>
       </c>
       <c r="E76">
-        <v>-23.02538591815414</v>
+        <v>-28.47035513786686</v>
       </c>
       <c r="F76">
-        <v>-2.296854206625031</v>
+        <v>-3.004312274944518</v>
       </c>
       <c r="G76">
-        <v>-11.51656144540798</v>
+        <v>-15.35020794061217</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.176990231931434</v>
       </c>
       <c r="E77">
-        <v>-23.29425047693755</v>
+        <v>-28.64372323677652</v>
       </c>
       <c r="F77">
-        <v>-2.465696192500641</v>
+        <v>-3.134395778410541</v>
       </c>
       <c r="G77">
-        <v>-11.94575712184679</v>
+        <v>-15.11783909393796</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.971158484229219</v>
       </c>
       <c r="E78">
-        <v>-23.63063458317531</v>
+        <v>-29.05963187506298</v>
       </c>
       <c r="F78">
-        <v>-2.438909275796313</v>
+        <v>-3.152974402520529</v>
       </c>
       <c r="G78">
-        <v>-11.22008222909301</v>
+        <v>-15.09829694361964</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.715216657153707</v>
       </c>
       <c r="E79">
-        <v>-23.35455163682368</v>
+        <v>-29.21935115331352</v>
       </c>
       <c r="F79">
-        <v>-2.371798262291108</v>
+        <v>-3.353376358075396</v>
       </c>
       <c r="G79">
-        <v>-11.66311267534043</v>
+        <v>-14.98177567227391</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.41193525708176</v>
       </c>
       <c r="E80">
-        <v>-24.45921852930677</v>
+        <v>-29.32594690298007</v>
       </c>
       <c r="F80">
-        <v>-2.522391314283044</v>
+        <v>-3.289258235996506</v>
       </c>
       <c r="G80">
-        <v>-10.90277637079048</v>
+        <v>-14.87426901643162</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.060431965426444</v>
       </c>
       <c r="E81">
-        <v>-24.460531786769</v>
+        <v>-29.84197104462811</v>
       </c>
       <c r="F81">
-        <v>-2.582126544433722</v>
+        <v>-3.339197193241677</v>
       </c>
       <c r="G81">
-        <v>-10.84091220629812</v>
+        <v>-14.55610572683442</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.67684946216879</v>
       </c>
       <c r="E82">
-        <v>-24.70768231268562</v>
+        <v>-30.05401910427428</v>
       </c>
       <c r="F82">
-        <v>-2.409357268701441</v>
+        <v>-3.338237115421832</v>
       </c>
       <c r="G82">
-        <v>-10.90376291336118</v>
+        <v>-15.12958822005683</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.267729082520875</v>
       </c>
       <c r="E83">
-        <v>-25.10337584300185</v>
+        <v>-30.35992658044043</v>
       </c>
       <c r="F83">
-        <v>-2.532290304746498</v>
+        <v>-3.509133452456385</v>
       </c>
       <c r="G83">
-        <v>-10.67324631691619</v>
+        <v>-14.79113459684944</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.841720262711594</v>
       </c>
       <c r="E84">
-        <v>-26.11046770604167</v>
+        <v>-31.14326427852425</v>
       </c>
       <c r="F84">
-        <v>-2.930143571167462</v>
+        <v>-3.412264168373011</v>
       </c>
       <c r="G84">
-        <v>-10.73538856723385</v>
+        <v>-14.76398150233634</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.420965766396489</v>
       </c>
       <c r="E85">
-        <v>-26.88072037848033</v>
+        <v>-31.87168743655406</v>
       </c>
       <c r="F85">
-        <v>-2.665433797398463</v>
+        <v>-3.458431568833235</v>
       </c>
       <c r="G85">
-        <v>-10.6069029843092</v>
+        <v>-14.49919082792327</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.011570645217398</v>
       </c>
       <c r="E86">
-        <v>-27.26629276938942</v>
+        <v>-32.17528991945031</v>
       </c>
       <c r="F86">
-        <v>-2.843786269425614</v>
+        <v>-3.682581161091559</v>
       </c>
       <c r="G86">
-        <v>-10.3225271224858</v>
+        <v>-14.6022199709237</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.629601809872047</v>
       </c>
       <c r="E87">
-        <v>-28.87431313324709</v>
+        <v>-33.40334187898339</v>
       </c>
       <c r="F87">
-        <v>-2.760217252361588</v>
+        <v>-3.695394348078062</v>
       </c>
       <c r="G87">
-        <v>-10.93201510899332</v>
+        <v>-14.62508094314514</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.291608038428466</v>
       </c>
       <c r="E88">
-        <v>-29.28805716095789</v>
+        <v>-33.633363451966</v>
       </c>
       <c r="F88">
-        <v>-2.866179525425492</v>
+        <v>-3.619986406666417</v>
       </c>
       <c r="G88">
-        <v>-10.4612753965822</v>
+        <v>-14.23734322849462</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.002886722703509</v>
       </c>
       <c r="E89">
-        <v>-30.57329242602283</v>
+        <v>-34.61734198367067</v>
       </c>
       <c r="F89">
-        <v>-2.899979400561921</v>
+        <v>-3.844814431827634</v>
       </c>
       <c r="G89">
-        <v>-10.31305896224348</v>
+        <v>-14.41655630071753</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.781168460126785</v>
       </c>
       <c r="E90">
-        <v>-31.49466706880846</v>
+        <v>-35.6765135620357</v>
       </c>
       <c r="F90">
-        <v>-2.872738538520859</v>
+        <v>-3.929104956899498</v>
       </c>
       <c r="G90">
-        <v>-10.59479300872654</v>
+        <v>-14.5655540238035</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.633424191082709</v>
       </c>
       <c r="E91">
-        <v>-32.73321603109132</v>
+        <v>-36.69610854181069</v>
       </c>
       <c r="F91">
-        <v>-3.002769854840506</v>
+        <v>-3.805584608365855</v>
       </c>
       <c r="G91">
-        <v>-10.59213464065851</v>
+        <v>-14.4157783225158</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.560784693011549</v>
       </c>
       <c r="E92">
-        <v>-33.89678478499219</v>
+        <v>-37.94195740419392</v>
       </c>
       <c r="F92">
-        <v>-3.328440842516326</v>
+        <v>-4.00803345977304</v>
       </c>
       <c r="G92">
-        <v>-10.56969907353887</v>
+        <v>-14.90848019403445</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.574066695754171</v>
       </c>
       <c r="E93">
-        <v>-34.76238674189935</v>
+        <v>-38.57646227554165</v>
       </c>
       <c r="F93">
-        <v>-3.43559844974247</v>
+        <v>-4.187898530677702</v>
       </c>
       <c r="G93">
-        <v>-10.94224138416413</v>
+        <v>-15.08430657817068</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.663582183898889</v>
       </c>
       <c r="E94">
-        <v>-36.49070375353378</v>
+        <v>-39.75694714409816</v>
       </c>
       <c r="F94">
-        <v>-3.26557852542008</v>
+        <v>-4.334623935265967</v>
       </c>
       <c r="G94">
-        <v>-11.31698189702747</v>
+        <v>-14.98015350495967</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.823734756566797</v>
       </c>
       <c r="E95">
-        <v>-38.19258126967443</v>
+        <v>-41.28596148618102</v>
       </c>
       <c r="F95">
-        <v>-3.448355307745582</v>
+        <v>-4.296557139637719</v>
       </c>
       <c r="G95">
-        <v>-11.29083189781277</v>
+        <v>-14.89242735871452</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.050002313160475</v>
       </c>
       <c r="E96">
-        <v>-39.56218200550227</v>
+        <v>-42.75865746126748</v>
       </c>
       <c r="F96">
-        <v>-3.621597581264862</v>
+        <v>-4.551714180517634</v>
       </c>
       <c r="G96">
-        <v>-11.4122262921923</v>
+        <v>-15.04687755030368</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.318429750743622</v>
       </c>
       <c r="E97">
-        <v>-41.06647993645126</v>
+        <v>-44.1893518399328</v>
       </c>
       <c r="F97">
-        <v>-3.653909708545863</v>
+        <v>-4.796374149669274</v>
       </c>
       <c r="G97">
-        <v>-11.79290261320756</v>
+        <v>-15.72212124758498</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.619580004304884</v>
       </c>
       <c r="E98">
-        <v>-42.61729888088104</v>
+        <v>-45.42687283861592</v>
       </c>
       <c r="F98">
-        <v>-3.827152810432546</v>
+        <v>-4.699504865585899</v>
       </c>
       <c r="G98">
-        <v>-11.89559242529021</v>
+        <v>-15.58265624037933</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.926858433216047</v>
       </c>
       <c r="E99">
-        <v>-44.44401283999115</v>
+        <v>-47.01182289164151</v>
       </c>
       <c r="F99">
-        <v>-3.97590191658585</v>
+        <v>-4.884805683387732</v>
       </c>
       <c r="G99">
-        <v>-11.99889799884317</v>
+        <v>-16.06230463083664</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.224414538339993</v>
       </c>
       <c r="E100">
-        <v>-46.16651529099973</v>
+        <v>-48.46007189979757</v>
       </c>
       <c r="F100">
-        <v>-4.081114517150221</v>
+        <v>-5.117692066643382</v>
       </c>
       <c r="G100">
-        <v>-12.40664796127859</v>
+        <v>-16.54981225640417</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.481409828835357</v>
       </c>
       <c r="E101">
-        <v>-48.20204850778853</v>
+        <v>-50.26049806729314</v>
       </c>
       <c r="F101">
-        <v>-4.123175700394769</v>
+        <v>-5.209688065296087</v>
       </c>
       <c r="G101">
-        <v>-12.8112197999963</v>
+        <v>-16.37982236405367</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.701471116065356</v>
       </c>
       <c r="E102">
-        <v>-50.27891763531935</v>
+        <v>-52.25349079925389</v>
       </c>
       <c r="F102">
-        <v>-4.287469949229009</v>
+        <v>-5.290977415267608</v>
       </c>
       <c r="G102">
-        <v>-12.96567661267654</v>
+        <v>-16.36115750830326</v>
       </c>
     </row>
   </sheetData>
